--- a/Course/Information/Schedule.xlsx
+++ b/Course/Information/Schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20384"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\csmith\Documents\GitHub\docpacs2627\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\csmith.PROG\Documents\GitHub\docpacs2627\Course\Information\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71B7E1DC-F52B-4818-9804-51E298B5D969}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC7203D4-1CAF-40B4-8E49-978520121268}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-165" windowWidth="29040" windowHeight="15720" xr2:uid="{E7498C5C-5E91-45C6-B3E9-69EC97B89725}"/>
   </bookViews>
@@ -28,43 +28,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="106">
   <si>
     <t>Week</t>
   </si>
   <si>
-    <t>In-Service Friday</t>
-  </si>
-  <si>
-    <t>TechLink Monday</t>
-  </si>
-  <si>
-    <t>Early-Dismissal Thursday</t>
-  </si>
-  <si>
-    <t>OAC Thursday
-2-Hour Delay Friday</t>
-  </si>
-  <si>
-    <t>Closed Monday</t>
-  </si>
-  <si>
-    <t>2-Hour Delay Wednesday</t>
-  </si>
-  <si>
-    <t>Early-Dismissal Friday</t>
-  </si>
-  <si>
-    <t>Early Dismissal Thursday
-In-Service Friday</t>
-  </si>
-  <si>
-    <t>Early Dismissal Friday</t>
-  </si>
-  <si>
-    <t>Fall Break Monday</t>
-  </si>
-  <si>
     <t>Fall Break Wednesday to Friday</t>
   </si>
   <si>
@@ -72,35 +40,6 @@
   </si>
   <si>
     <t>Early Dismissal Thursday</t>
-  </si>
-  <si>
-    <t>Closed Friday</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Closed </t>
-  </si>
-  <si>
-    <t>In-Service Monday and Tuesday</t>
-  </si>
-  <si>
-    <t>Make-Up Day Thursday
-Closed Friday</t>
-  </si>
-  <si>
-    <t>Closed Monday
-Early Dismissal Friday</t>
-  </si>
-  <si>
-    <t>NOCTI Friday</t>
-  </si>
-  <si>
-    <t>NOCTI Monday</t>
-  </si>
-  <si>
-    <t>New-Student Orientation Thursday</t>
-  </si>
-  <si>
-    <t>Early Dismissal Thursday and Friday</t>
   </si>
   <si>
     <t>Days</t>
@@ -325,6 +264,152 @@
   <si>
     <t>Company Projects
 NOCTI Prep</t>
+  </si>
+  <si>
+    <t>Intervention (B) Wednesday</t>
+  </si>
+  <si>
+    <t>Intervention (A) Wednesday</t>
+  </si>
+  <si>
+    <t>Early-Dismissal Thursday
+Intervention (B) Wednesday</t>
+  </si>
+  <si>
+    <t>Closed Monday
+Intervention (B) Wednesday</t>
+  </si>
+  <si>
+    <t>Early-Dismissal Friday
+Intervention (B) Wednesday</t>
+  </si>
+  <si>
+    <t>Early Dismissal Thursday
+In-Service Friday
+Intervention (B) Wednesday</t>
+  </si>
+  <si>
+    <t>Early Dismissal Friday
+Intervention (B) Wednesday</t>
+  </si>
+  <si>
+    <t>Fall Break Monday
+Intervention (B) Wednesday</t>
+  </si>
+  <si>
+    <t>In-Service Monday and Tuesday
+Intervention (B) Wednesday</t>
+  </si>
+  <si>
+    <t>Intervention (B) Wednesday
+Intervention (A) Thursday</t>
+  </si>
+  <si>
+    <t>Early Dismissal Thursday
+Intervention (A) Wednesday</t>
+  </si>
+  <si>
+    <t>Closed Monday
+Early Dismissal Friday
+Intervention (B) Wednesday</t>
+  </si>
+  <si>
+    <t>NOCTI Friday
+Intervention (A) Wednesday</t>
+  </si>
+  <si>
+    <t>NOCTI Monday
+Intervention (B) Wednesday</t>
+  </si>
+  <si>
+    <t>Early Dismissal Friday
+Intervention (A) Wednesday</t>
+  </si>
+  <si>
+    <t>In-service Friday
+Intervention (B) Wednesday</t>
+  </si>
+  <si>
+    <t>New-Student Orientation Thursday
+Intervention (B) Wednesday</t>
+  </si>
+  <si>
+    <t>Make-Up Day Thursday
+Closed Friday
+Intervention (B) Wednesday</t>
+  </si>
+  <si>
+    <t>Techlink Friday
+Intervention (A) Wednesday</t>
+  </si>
+  <si>
+    <t>Junior Picture Day Tuesday
+Senior Picture Day
+Intervention (B) Wednesday</t>
+  </si>
+  <si>
+    <t>Picture Day Retakes Monday
+Parent Conferences Thursday
+OAC Thursday
+2-Hour Delay Friday
+Intervention (A) Wednesday</t>
+  </si>
+  <si>
+    <t>Senior Pre-NOCTI
+Intervention (B) Wednesday</t>
+  </si>
+  <si>
+    <t>Closed Monday
+Senior Class Meeting Wednesday
+Intervention (B) Wednesday
+Intervention (A) Thursday</t>
+  </si>
+  <si>
+    <t>Intervention (A) Wednesday
+Open House Thursday</t>
+  </si>
+  <si>
+    <t>Intervention (A) Wednesday
+Junior Pre-NOCTI</t>
+  </si>
+  <si>
+    <t>Intervention (B) Wednesday
+Junior Pre-NOCTI Makeups</t>
+  </si>
+  <si>
+    <t>Intervention (B) Tuesday
+Intervention (A) Wednesday
+Quarter 2 Ends Thursday</t>
+  </si>
+  <si>
+    <t>2-Hour Delay Wednesday
+Senior Pre-NOCTI Makeup
+Quarter 1 Ends Tuesday</t>
+  </si>
+  <si>
+    <t>Parent Conferences Thursday
+Closed Friday
+Intervention (A) Wednesday</t>
+  </si>
+  <si>
+    <t>Quarter 3 Ends Tuesday
+2-Hour Delay Wednesday
+Intervention (A) Monday</t>
+  </si>
+  <si>
+    <t>Senior Cap &amp; Gown Monday
+In-Service Friday
+Intervention (B) Wednesday</t>
+  </si>
+  <si>
+    <t>Quarter 4 Ends Friday
+Early Dismissal Thursday and Friday</t>
+  </si>
+  <si>
+    <t>Keystone Exams</t>
+  </si>
+  <si>
+    <t>First Day Wednesday</t>
   </si>
 </sst>
 </file>
@@ -699,34 +784,34 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="B1" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="C1" t="s">
         <v>0</v>
       </c>
       <c r="D1" t="s">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="E1" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="H1" t="s">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="I1" t="s">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="J1" t="s">
-        <v>87</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="45" x14ac:dyDescent="0.25">
@@ -745,14 +830,17 @@
       <c r="E2">
         <v>3</v>
       </c>
+      <c r="F2" t="s">
+        <v>105</v>
+      </c>
       <c r="G2" s="1" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>22808</v>
       </c>
@@ -768,14 +856,17 @@
       <c r="E3">
         <v>5</v>
       </c>
+      <c r="F3" s="1" t="s">
+        <v>91</v>
+      </c>
       <c r="G3" s="1" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="H3" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="I3" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="30" x14ac:dyDescent="0.25">
@@ -794,17 +885,17 @@
       <c r="E4">
         <v>4</v>
       </c>
-      <c r="F4" t="s">
-        <v>1</v>
+      <c r="F4" s="1" t="s">
+        <v>90</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="H4" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="I4" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="30" x14ac:dyDescent="0.25">
@@ -823,14 +914,14 @@
       <c r="E5">
         <v>4</v>
       </c>
-      <c r="F5" t="s">
-        <v>2</v>
+      <c r="F5" s="1" t="s">
+        <v>75</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="H5" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="30" x14ac:dyDescent="0.25">
@@ -849,14 +940,17 @@
       <c r="E6">
         <v>5</v>
       </c>
+      <c r="F6" t="s">
+        <v>73</v>
+      </c>
       <c r="G6" s="1" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="H6" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="I6" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="30" x14ac:dyDescent="0.25">
@@ -875,20 +969,20 @@
       <c r="E7">
         <v>4.5</v>
       </c>
-      <c r="F7" t="s">
-        <v>3</v>
+      <c r="F7" s="1" t="s">
+        <v>74</v>
       </c>
       <c r="G7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I7" t="s">
         <v>29</v>
       </c>
-      <c r="H7" t="s">
-        <v>43</v>
-      </c>
-      <c r="I7" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>70210</v>
       </c>
@@ -905,19 +999,19 @@
         <v>4.5</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>4</v>
+        <v>92</v>
       </c>
       <c r="G8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I8" t="s">
         <v>30</v>
       </c>
-      <c r="H8" t="s">
-        <v>43</v>
-      </c>
-      <c r="I8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>80910</v>
       </c>
@@ -933,17 +1027,20 @@
       <c r="E9">
         <v>5</v>
       </c>
+      <c r="F9" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="G9" t="s">
+        <v>12</v>
+      </c>
+      <c r="H9" t="s">
+        <v>24</v>
+      </c>
+      <c r="I9" t="s">
         <v>31</v>
       </c>
-      <c r="H9" t="s">
-        <v>43</v>
-      </c>
-      <c r="I9" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>91610</v>
       </c>
@@ -959,17 +1056,17 @@
       <c r="E10">
         <v>4</v>
       </c>
-      <c r="F10" t="s">
-        <v>5</v>
+      <c r="F10" s="1" t="s">
+        <v>94</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="H10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>102310</v>
       </c>
@@ -985,17 +1082,17 @@
       <c r="E11">
         <v>4.5</v>
       </c>
-      <c r="F11" t="s">
-        <v>6</v>
+      <c r="F11" s="1" t="s">
+        <v>99</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="H11" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="I11" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="30" x14ac:dyDescent="0.25">
@@ -1014,14 +1111,14 @@
       <c r="E12">
         <v>4.5</v>
       </c>
-      <c r="F12" t="s">
-        <v>7</v>
+      <c r="F12" s="1" t="s">
+        <v>76</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="H12" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="30" x14ac:dyDescent="0.25">
@@ -1040,17 +1137,20 @@
       <c r="E13">
         <v>5</v>
       </c>
+      <c r="F13" s="1" t="s">
+        <v>95</v>
+      </c>
       <c r="G13" s="1" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="H13" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="I13" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>131311</v>
       </c>
@@ -1067,16 +1167,16 @@
         <v>3.5</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>8</v>
+        <v>77</v>
       </c>
       <c r="G14" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="H14" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="I14" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="30" x14ac:dyDescent="0.25">
@@ -1095,17 +1195,17 @@
       <c r="E15">
         <v>4.5</v>
       </c>
-      <c r="F15" t="s">
-        <v>9</v>
+      <c r="F15" s="1" t="s">
+        <v>78</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="H15" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="I15" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
@@ -1125,17 +1225,17 @@
         <v>2</v>
       </c>
       <c r="F16" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G16" s="1"/>
       <c r="H16" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="I16" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>160412</v>
       </c>
@@ -1151,20 +1251,20 @@
       <c r="E17">
         <v>4</v>
       </c>
-      <c r="F17" t="s">
-        <v>10</v>
+      <c r="F17" s="1" t="s">
+        <v>79</v>
       </c>
       <c r="G17" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="H17" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="I17" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>171112</v>
       </c>
@@ -1180,17 +1280,20 @@
       <c r="E18">
         <v>5</v>
       </c>
+      <c r="F18" s="1" t="s">
+        <v>96</v>
+      </c>
       <c r="G18" s="1" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="H18" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="I18" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>181812</v>
       </c>
@@ -1206,14 +1309,17 @@
       <c r="E19">
         <v>5</v>
       </c>
+      <c r="F19" s="1" t="s">
+        <v>97</v>
+      </c>
       <c r="G19" s="1" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="H19" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="I19" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -1233,19 +1339,19 @@
         <v>2</v>
       </c>
       <c r="F20" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="H20" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="I20" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>200801</v>
       </c>
@@ -1261,17 +1367,20 @@
       <c r="E21">
         <v>5</v>
       </c>
+      <c r="F21" s="1" t="s">
+        <v>98</v>
+      </c>
       <c r="G21" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="H21" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="I21" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>211501</v>
       </c>
@@ -1287,20 +1396,20 @@
       <c r="E22">
         <v>3</v>
       </c>
-      <c r="F22" t="s">
-        <v>16</v>
+      <c r="F22" s="1" t="s">
+        <v>80</v>
       </c>
       <c r="G22" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="H22" t="s">
+        <v>24</v>
+      </c>
+      <c r="I22" t="s">
         <v>43</v>
       </c>
-      <c r="I22" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>222201</v>
       </c>
@@ -1316,20 +1425,20 @@
       <c r="E23">
         <v>4</v>
       </c>
-      <c r="F23" t="s">
-        <v>5</v>
+      <c r="F23" s="1" t="s">
+        <v>75</v>
       </c>
       <c r="G23" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="H23" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="I23" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>232901</v>
       </c>
@@ -1345,14 +1454,14 @@
       <c r="E24">
         <v>4.5</v>
       </c>
-      <c r="F24" t="s">
-        <v>13</v>
+      <c r="F24" s="1" t="s">
+        <v>82</v>
       </c>
       <c r="G24" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="H24" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
@@ -1371,14 +1480,17 @@
       <c r="E25">
         <v>5</v>
       </c>
+      <c r="F25" s="1" t="s">
+        <v>72</v>
+      </c>
       <c r="G25" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="H25" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="I25" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="45" x14ac:dyDescent="0.25">
@@ -1397,17 +1509,17 @@
       <c r="E26">
         <v>4</v>
       </c>
-      <c r="F26" t="s">
-        <v>14</v>
+      <c r="F26" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="H26" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="I26" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="45" x14ac:dyDescent="0.25">
@@ -1426,17 +1538,17 @@
       <c r="E27">
         <v>4</v>
       </c>
-      <c r="F27" t="s">
-        <v>5</v>
+      <c r="F27" s="1" t="s">
+        <v>75</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="H27" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="I27" t="s">
-        <v>66</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
@@ -1456,16 +1568,16 @@
         <v>4.5</v>
       </c>
       <c r="F28" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="G28" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="H28" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>280403</v>
       </c>
@@ -1481,17 +1593,17 @@
       <c r="E29">
         <v>4</v>
       </c>
-      <c r="F29" t="s">
-        <v>15</v>
+      <c r="F29" s="1" t="s">
+        <v>87</v>
       </c>
       <c r="G29" t="s">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="H29" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="I29" t="s">
-        <v>67</v>
+        <v>48</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -1510,17 +1622,20 @@
       <c r="E30">
         <v>5</v>
       </c>
+      <c r="F30" s="1" t="s">
+        <v>81</v>
+      </c>
       <c r="G30" s="1" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="H30" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="I30" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>301903</v>
       </c>
@@ -1536,20 +1651,20 @@
       <c r="E31">
         <v>4.5</v>
       </c>
-      <c r="F31" t="s">
-        <v>6</v>
+      <c r="F31" s="1" t="s">
+        <v>101</v>
       </c>
       <c r="G31" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="H31" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="I31" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>312403</v>
       </c>
@@ -1566,16 +1681,16 @@
         <v>3</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>17</v>
+        <v>89</v>
       </c>
       <c r="G32" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="H32" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>320204</v>
       </c>
@@ -1592,19 +1707,19 @@
         <v>3.5</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>18</v>
+        <v>83</v>
       </c>
       <c r="G33" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="I33" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>330804</v>
       </c>
@@ -1620,20 +1735,20 @@
       <c r="E34">
         <v>4</v>
       </c>
-      <c r="F34" t="s">
-        <v>19</v>
+      <c r="F34" s="1" t="s">
+        <v>84</v>
       </c>
       <c r="G34" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="H34" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="I34" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>341604</v>
       </c>
@@ -1649,20 +1764,20 @@
       <c r="E35">
         <v>4</v>
       </c>
-      <c r="F35" t="s">
-        <v>20</v>
+      <c r="F35" s="1" t="s">
+        <v>85</v>
       </c>
       <c r="G35" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="H35" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="I35" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>352304</v>
       </c>
@@ -1678,20 +1793,20 @@
       <c r="E36">
         <v>4.5</v>
       </c>
-      <c r="F36" t="s">
-        <v>9</v>
+      <c r="F36" s="1" t="s">
+        <v>86</v>
       </c>
       <c r="G36" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="H36" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="I36" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>362904</v>
       </c>
@@ -1707,17 +1822,17 @@
       <c r="E37">
         <v>4</v>
       </c>
-      <c r="F37" t="s">
-        <v>1</v>
+      <c r="F37" s="1" t="s">
+        <v>102</v>
       </c>
       <c r="G37" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="H37" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>370705</v>
       </c>
@@ -1733,14 +1848,14 @@
       <c r="E38">
         <v>5</v>
       </c>
-      <c r="F38" t="s">
-        <v>21</v>
+      <c r="F38" s="1" t="s">
+        <v>88</v>
       </c>
       <c r="G38" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="H38" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
@@ -1759,14 +1874,17 @@
       <c r="E39">
         <v>5</v>
       </c>
+      <c r="F39" s="1" t="s">
+        <v>104</v>
+      </c>
       <c r="G39" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="H39" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>392105</v>
       </c>
@@ -1782,14 +1900,14 @@
       <c r="E40">
         <v>4</v>
       </c>
-      <c r="F40" t="s">
-        <v>22</v>
+      <c r="F40" s="1" t="s">
+        <v>103</v>
       </c>
       <c r="G40" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="H40" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
